--- a/spm/file/23计算机12考勤表.xlsx
+++ b/spm/file/23计算机12考勤表.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{587785AF-7B2C-498A-B884-C34467775C6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="2250" windowWidth="21600" windowHeight="11295" xr2:uid="{FC895020-1FB2-46FE-9EB0-1A2B1386E4D8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FC895020-1FB2-46FE-9EB0-1A2B1386E4D8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1002,15 +1002,33 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="18">
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1029,25 +1047,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1415,250 +1415,250 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="6"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="6"/>
-      <c r="AF1" s="6"/>
-      <c r="AG1" s="6"/>
-      <c r="AH1" s="6"/>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="6"/>
-      <c r="AK1" s="6"/>
-      <c r="AL1" s="6"/>
-      <c r="AM1" s="7"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="12"/>
+      <c r="AC1" s="12"/>
+      <c r="AD1" s="12"/>
+      <c r="AE1" s="12"/>
+      <c r="AF1" s="12"/>
+      <c r="AG1" s="12"/>
+      <c r="AH1" s="12"/>
+      <c r="AI1" s="12"/>
+      <c r="AJ1" s="12"/>
+      <c r="AK1" s="12"/>
+      <c r="AL1" s="12"/>
+      <c r="AM1" s="13"/>
     </row>
     <row r="2" spans="1:39" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-      <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
-      <c r="P2" s="9"/>
-      <c r="Q2" s="9"/>
-      <c r="R2" s="9"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
-      <c r="W2" s="9"/>
-      <c r="X2" s="9"/>
-      <c r="Y2" s="9"/>
-      <c r="Z2" s="9"/>
-      <c r="AA2" s="9"/>
-      <c r="AB2" s="9"/>
-      <c r="AC2" s="9"/>
-      <c r="AD2" s="9"/>
-      <c r="AE2" s="9"/>
-      <c r="AF2" s="9"/>
-      <c r="AG2" s="9"/>
-      <c r="AH2" s="9"/>
-      <c r="AI2" s="9"/>
-      <c r="AJ2" s="9"/>
-      <c r="AK2" s="9"/>
-      <c r="AL2" s="9"/>
-      <c r="AM2" s="10"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
+      <c r="X2" s="15"/>
+      <c r="Y2" s="15"/>
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15"/>
+      <c r="AB2" s="15"/>
+      <c r="AC2" s="15"/>
+      <c r="AD2" s="15"/>
+      <c r="AE2" s="15"/>
+      <c r="AF2" s="15"/>
+      <c r="AG2" s="15"/>
+      <c r="AH2" s="15"/>
+      <c r="AI2" s="15"/>
+      <c r="AJ2" s="15"/>
+      <c r="AK2" s="15"/>
+      <c r="AL2" s="15"/>
+      <c r="AM2" s="16"/>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.15">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="15" t="s">
+      <c r="D3" s="6"/>
+      <c r="E3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="6"/>
+      <c r="G3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="I3" s="15" t="s">
+      <c r="H3" s="6"/>
+      <c r="I3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="15" t="s">
+      <c r="J3" s="6"/>
+      <c r="K3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="14"/>
-      <c r="M3" s="15" t="s">
+      <c r="L3" s="6"/>
+      <c r="M3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="14"/>
-      <c r="O3" s="15" t="s">
+      <c r="N3" s="6"/>
+      <c r="O3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="15" t="s">
+      <c r="P3" s="6"/>
+      <c r="Q3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="R3" s="14"/>
-      <c r="S3" s="15" t="s">
+      <c r="R3" s="6"/>
+      <c r="S3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="14"/>
-      <c r="U3" s="15" t="s">
+      <c r="T3" s="6"/>
+      <c r="U3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="V3" s="14"/>
-      <c r="W3" s="15" t="s">
+      <c r="V3" s="6"/>
+      <c r="W3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="X3" s="14"/>
-      <c r="Y3" s="15" t="s">
+      <c r="X3" s="6"/>
+      <c r="Y3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="15" t="s">
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="15" t="s">
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="15" t="s">
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AF3" s="14"/>
-      <c r="AG3" s="15" t="s">
+      <c r="AF3" s="6"/>
+      <c r="AG3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AH3" s="14"/>
-      <c r="AI3" s="15" t="s">
+      <c r="AH3" s="6"/>
+      <c r="AI3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AJ3" s="14"/>
-      <c r="AK3" s="15" t="s">
+      <c r="AJ3" s="6"/>
+      <c r="AK3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AL3" s="16"/>
-      <c r="AM3" s="11" t="s">
+      <c r="AL3" s="7"/>
+      <c r="AM3" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.15">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="13" t="s">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="15" t="s">
+      <c r="D4" s="6"/>
+      <c r="E4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="15" t="s">
+      <c r="F4" s="6"/>
+      <c r="G4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="15" t="s">
+      <c r="H4" s="6"/>
+      <c r="I4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="15" t="s">
+      <c r="J4" s="6"/>
+      <c r="K4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="14"/>
-      <c r="M4" s="15" t="s">
+      <c r="L4" s="6"/>
+      <c r="M4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="14"/>
-      <c r="O4" s="15" t="s">
+      <c r="N4" s="6"/>
+      <c r="O4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="15" t="s">
+      <c r="P4" s="6"/>
+      <c r="Q4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="R4" s="14"/>
-      <c r="S4" s="15" t="s">
+      <c r="R4" s="6"/>
+      <c r="S4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="T4" s="14"/>
-      <c r="U4" s="15" t="s">
+      <c r="T4" s="6"/>
+      <c r="U4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="V4" s="14"/>
-      <c r="W4" s="15" t="s">
+      <c r="V4" s="6"/>
+      <c r="W4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="15" t="s">
+      <c r="X4" s="6"/>
+      <c r="Y4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="15" t="s">
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AB4" s="14"/>
-      <c r="AC4" s="15" t="s">
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="15" t="s">
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AF4" s="14"/>
-      <c r="AG4" s="15" t="s">
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AH4" s="14"/>
-      <c r="AI4" s="15" t="s">
+      <c r="AH4" s="6"/>
+      <c r="AI4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AJ4" s="14"/>
-      <c r="AK4" s="15" t="s">
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AL4" s="16"/>
-      <c r="AM4" s="17"/>
+      <c r="AL4" s="7"/>
+      <c r="AM4" s="9"/>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
@@ -2876,250 +2876,250 @@
       <c r="AM31" s="2"/>
     </row>
     <row r="32" spans="1:39" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="6"/>
-      <c r="O32" s="6"/>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="6"/>
-      <c r="S32" s="6"/>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6"/>
-      <c r="V32" s="6"/>
-      <c r="W32" s="6"/>
-      <c r="X32" s="6"/>
-      <c r="Y32" s="6"/>
-      <c r="Z32" s="6"/>
-      <c r="AA32" s="6"/>
-      <c r="AB32" s="6"/>
-      <c r="AC32" s="6"/>
-      <c r="AD32" s="6"/>
-      <c r="AE32" s="6"/>
-      <c r="AF32" s="6"/>
-      <c r="AG32" s="6"/>
-      <c r="AH32" s="6"/>
-      <c r="AI32" s="6"/>
-      <c r="AJ32" s="6"/>
-      <c r="AK32" s="6"/>
-      <c r="AL32" s="6"/>
-      <c r="AM32" s="7"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="12"/>
+      <c r="Q32" s="12"/>
+      <c r="R32" s="12"/>
+      <c r="S32" s="12"/>
+      <c r="T32" s="12"/>
+      <c r="U32" s="12"/>
+      <c r="V32" s="12"/>
+      <c r="W32" s="12"/>
+      <c r="X32" s="12"/>
+      <c r="Y32" s="12"/>
+      <c r="Z32" s="12"/>
+      <c r="AA32" s="12"/>
+      <c r="AB32" s="12"/>
+      <c r="AC32" s="12"/>
+      <c r="AD32" s="12"/>
+      <c r="AE32" s="12"/>
+      <c r="AF32" s="12"/>
+      <c r="AG32" s="12"/>
+      <c r="AH32" s="12"/>
+      <c r="AI32" s="12"/>
+      <c r="AJ32" s="12"/>
+      <c r="AK32" s="12"/>
+      <c r="AL32" s="12"/>
+      <c r="AM32" s="13"/>
     </row>
     <row r="33" spans="1:39" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
-      <c r="P33" s="9"/>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="9"/>
-      <c r="S33" s="9"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="9"/>
-      <c r="AA33" s="9"/>
-      <c r="AB33" s="9"/>
-      <c r="AC33" s="9"/>
-      <c r="AD33" s="9"/>
-      <c r="AE33" s="9"/>
-      <c r="AF33" s="9"/>
-      <c r="AG33" s="9"/>
-      <c r="AH33" s="9"/>
-      <c r="AI33" s="9"/>
-      <c r="AJ33" s="9"/>
-      <c r="AK33" s="9"/>
-      <c r="AL33" s="9"/>
-      <c r="AM33" s="10"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="15"/>
+      <c r="S33" s="15"/>
+      <c r="T33" s="15"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="15"/>
+      <c r="W33" s="15"/>
+      <c r="X33" s="15"/>
+      <c r="Y33" s="15"/>
+      <c r="Z33" s="15"/>
+      <c r="AA33" s="15"/>
+      <c r="AB33" s="15"/>
+      <c r="AC33" s="15"/>
+      <c r="AD33" s="15"/>
+      <c r="AE33" s="15"/>
+      <c r="AF33" s="15"/>
+      <c r="AG33" s="15"/>
+      <c r="AH33" s="15"/>
+      <c r="AI33" s="15"/>
+      <c r="AJ33" s="15"/>
+      <c r="AK33" s="15"/>
+      <c r="AL33" s="15"/>
+      <c r="AM33" s="16"/>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.15">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="15" t="s">
+      <c r="D34" s="6"/>
+      <c r="E34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="15" t="s">
+      <c r="F34" s="6"/>
+      <c r="G34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="s">
+      <c r="H34" s="6"/>
+      <c r="I34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="J34" s="14"/>
-      <c r="K34" s="15" t="s">
+      <c r="J34" s="6"/>
+      <c r="K34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L34" s="14"/>
-      <c r="M34" s="15" t="s">
+      <c r="L34" s="6"/>
+      <c r="M34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="N34" s="14"/>
-      <c r="O34" s="15" t="s">
+      <c r="N34" s="6"/>
+      <c r="O34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="P34" s="14"/>
-      <c r="Q34" s="15" t="s">
+      <c r="P34" s="6"/>
+      <c r="Q34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="R34" s="14"/>
-      <c r="S34" s="15" t="s">
+      <c r="R34" s="6"/>
+      <c r="S34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="T34" s="14"/>
-      <c r="U34" s="15" t="s">
+      <c r="T34" s="6"/>
+      <c r="U34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="V34" s="14"/>
-      <c r="W34" s="15" t="s">
+      <c r="V34" s="6"/>
+      <c r="W34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="X34" s="14"/>
-      <c r="Y34" s="15" t="s">
+      <c r="X34" s="6"/>
+      <c r="Y34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="Z34" s="14"/>
-      <c r="AA34" s="15" t="s">
+      <c r="Z34" s="6"/>
+      <c r="AA34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AB34" s="14"/>
-      <c r="AC34" s="15" t="s">
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AD34" s="14"/>
-      <c r="AE34" s="15" t="s">
+      <c r="AD34" s="6"/>
+      <c r="AE34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AF34" s="14"/>
-      <c r="AG34" s="15" t="s">
+      <c r="AF34" s="6"/>
+      <c r="AG34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AH34" s="14"/>
-      <c r="AI34" s="15" t="s">
+      <c r="AH34" s="6"/>
+      <c r="AI34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AJ34" s="14"/>
-      <c r="AK34" s="15" t="s">
+      <c r="AJ34" s="6"/>
+      <c r="AK34" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="AL34" s="16"/>
-      <c r="AM34" s="11" t="s">
+      <c r="AL34" s="7"/>
+      <c r="AM34" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:39" x14ac:dyDescent="0.15">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="13" t="s">
+      <c r="A35" s="17"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="15" t="s">
+      <c r="D35" s="6"/>
+      <c r="E35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="F35" s="14"/>
-      <c r="G35" s="15" t="s">
+      <c r="F35" s="6"/>
+      <c r="G35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="s">
+      <c r="H35" s="6"/>
+      <c r="I35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J35" s="14"/>
-      <c r="K35" s="15" t="s">
+      <c r="J35" s="6"/>
+      <c r="K35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="L35" s="14"/>
-      <c r="M35" s="15" t="s">
+      <c r="L35" s="6"/>
+      <c r="M35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="N35" s="14"/>
-      <c r="O35" s="15" t="s">
+      <c r="N35" s="6"/>
+      <c r="O35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="P35" s="14"/>
-      <c r="Q35" s="15" t="s">
+      <c r="P35" s="6"/>
+      <c r="Q35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="R35" s="14"/>
-      <c r="S35" s="15" t="s">
+      <c r="R35" s="6"/>
+      <c r="S35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="T35" s="14"/>
-      <c r="U35" s="15" t="s">
+      <c r="T35" s="6"/>
+      <c r="U35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="V35" s="14"/>
-      <c r="W35" s="15" t="s">
+      <c r="V35" s="6"/>
+      <c r="W35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="X35" s="14"/>
-      <c r="Y35" s="15" t="s">
+      <c r="X35" s="6"/>
+      <c r="Y35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="Z35" s="14"/>
-      <c r="AA35" s="15" t="s">
+      <c r="Z35" s="6"/>
+      <c r="AA35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AB35" s="14"/>
-      <c r="AC35" s="15" t="s">
+      <c r="AB35" s="6"/>
+      <c r="AC35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AD35" s="14"/>
-      <c r="AE35" s="15" t="s">
+      <c r="AD35" s="6"/>
+      <c r="AE35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AF35" s="14"/>
-      <c r="AG35" s="15" t="s">
+      <c r="AF35" s="6"/>
+      <c r="AG35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AH35" s="14"/>
-      <c r="AI35" s="15" t="s">
+      <c r="AH35" s="6"/>
+      <c r="AI35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AJ35" s="14"/>
-      <c r="AK35" s="15" t="s">
+      <c r="AJ35" s="6"/>
+      <c r="AK35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="AL35" s="16"/>
-      <c r="AM35" s="17"/>
+      <c r="AL35" s="7"/>
+      <c r="AM35" s="9"/>
     </row>
     <row r="36" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
@@ -4032,18 +4032,60 @@
     </row>
   </sheetData>
   <mergeCells count="82">
-    <mergeCell ref="AA35:AB35"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
-    <mergeCell ref="AK35:AL35"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="S35:T35"/>
-    <mergeCell ref="U35:V35"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="Y35:Z35"/>
+    <mergeCell ref="A1:AM1"/>
+    <mergeCell ref="A2:AM2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="AK3:AL3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:X3"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AM3:AM4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="AI4:AJ4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="A32:AM32"/>
+    <mergeCell ref="A33:AM33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="AC4:AD4"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:R34"/>
     <mergeCell ref="AG34:AH34"/>
     <mergeCell ref="AI34:AJ34"/>
     <mergeCell ref="AK34:AL34"/>
@@ -4060,64 +4102,22 @@
     <mergeCell ref="AA34:AB34"/>
     <mergeCell ref="AC34:AD34"/>
     <mergeCell ref="AE34:AF34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="S34:T34"/>
-    <mergeCell ref="AG4:AH4"/>
-    <mergeCell ref="AI4:AJ4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="A32:AM32"/>
-    <mergeCell ref="A33:AM33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AC4:AD4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="AK3:AL3"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="Q3:R3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="W3:X3"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="A1:AM1"/>
-    <mergeCell ref="A2:AM2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="AK35:AL35"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="U35:V35"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="Y35:Z35"/>
+    <mergeCell ref="AA35:AB35"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.38" right="0.33" top="0.62" bottom="0.73" header="0.4" footer="0.35"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;R&amp;10教师签字:__________________                         系(教研室主任签字):__________________       </oddFooter>
   </headerFooter>
@@ -4127,7 +4127,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CFC7B64-F5C0-44D5-8E84-41FFCCCBA224}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4137,7 +4137,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA4BFE85-988E-4B7F-A442-5E8EA9C632DA}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/spm/file/23计算机12考勤表.xlsx
+++ b/spm/file/23计算机12考勤表.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -1011,89 +1011,89 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 着色 6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 着色 6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 着色 6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="标题" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="标题 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="标题 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="标题 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="检查单元格" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="解释性文本" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="警告文本" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="链接单元格" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="适中" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="输出" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="输入" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="着色 1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="着色 2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="着色 3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="着色 4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="着色 5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="着色 6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="注释" xfId="15" builtinId="10" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1109,7 +1109,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1415,250 +1415,250 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
-      <c r="AA1" s="12"/>
-      <c r="AB1" s="12"/>
-      <c r="AC1" s="12"/>
-      <c r="AD1" s="12"/>
-      <c r="AE1" s="12"/>
-      <c r="AF1" s="12"/>
-      <c r="AG1" s="12"/>
-      <c r="AH1" s="12"/>
-      <c r="AI1" s="12"/>
-      <c r="AJ1" s="12"/>
-      <c r="AK1" s="12"/>
-      <c r="AL1" s="12"/>
-      <c r="AM1" s="13"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6"/>
+      <c r="AD1" s="6"/>
+      <c r="AE1" s="6"/>
+      <c r="AF1" s="6"/>
+      <c r="AG1" s="6"/>
+      <c r="AH1" s="6"/>
+      <c r="AI1" s="6"/>
+      <c r="AJ1" s="6"/>
+      <c r="AK1" s="6"/>
+      <c r="AL1" s="6"/>
+      <c r="AM1" s="7"/>
     </row>
     <row r="2" spans="1:39" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="15"/>
-      <c r="V2" s="15"/>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="15"/>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
-      <c r="AC2" s="15"/>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="15"/>
-      <c r="AI2" s="15"/>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="15"/>
-      <c r="AL2" s="15"/>
-      <c r="AM2" s="16"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9"/>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9"/>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9"/>
+      <c r="AJ2" s="9"/>
+      <c r="AK2" s="9"/>
+      <c r="AL2" s="9"/>
+      <c r="AM2" s="10"/>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.15">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="14"/>
+      <c r="E3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="5" t="s">
+      <c r="F3" s="14"/>
+      <c r="G3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="5" t="s">
+      <c r="H3" s="14"/>
+      <c r="I3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="5" t="s">
+      <c r="J3" s="14"/>
+      <c r="K3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="6"/>
-      <c r="M3" s="5" t="s">
+      <c r="L3" s="14"/>
+      <c r="M3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="5" t="s">
+      <c r="N3" s="14"/>
+      <c r="O3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="5" t="s">
+      <c r="P3" s="14"/>
+      <c r="Q3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="R3" s="6"/>
-      <c r="S3" s="5" t="s">
+      <c r="R3" s="14"/>
+      <c r="S3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="6"/>
-      <c r="U3" s="5" t="s">
+      <c r="T3" s="14"/>
+      <c r="U3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="V3" s="6"/>
-      <c r="W3" s="5" t="s">
+      <c r="V3" s="14"/>
+      <c r="W3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="5" t="s">
+      <c r="X3" s="14"/>
+      <c r="Y3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="5" t="s">
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="5" t="s">
+      <c r="AB3" s="14"/>
+      <c r="AC3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="5" t="s">
+      <c r="AD3" s="14"/>
+      <c r="AE3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="AF3" s="6"/>
-      <c r="AG3" s="5" t="s">
+      <c r="AF3" s="14"/>
+      <c r="AG3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="AH3" s="6"/>
-      <c r="AI3" s="5" t="s">
+      <c r="AH3" s="14"/>
+      <c r="AI3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="AJ3" s="6"/>
-      <c r="AK3" s="5" t="s">
+      <c r="AJ3" s="14"/>
+      <c r="AK3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="AL3" s="7"/>
-      <c r="AM3" s="8" t="s">
+      <c r="AL3" s="16"/>
+      <c r="AM3" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.15">
-      <c r="A4" s="17"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="10" t="s">
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="14"/>
+      <c r="E4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="5" t="s">
+      <c r="F4" s="14"/>
+      <c r="G4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="5" t="s">
+      <c r="H4" s="14"/>
+      <c r="I4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="5" t="s">
+      <c r="J4" s="14"/>
+      <c r="K4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="6"/>
-      <c r="M4" s="5" t="s">
+      <c r="L4" s="14"/>
+      <c r="M4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="N4" s="6"/>
-      <c r="O4" s="5" t="s">
+      <c r="N4" s="14"/>
+      <c r="O4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="5" t="s">
+      <c r="P4" s="14"/>
+      <c r="Q4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="R4" s="6"/>
-      <c r="S4" s="5" t="s">
+      <c r="R4" s="14"/>
+      <c r="S4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="T4" s="6"/>
-      <c r="U4" s="5" t="s">
+      <c r="T4" s="14"/>
+      <c r="U4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="V4" s="6"/>
-      <c r="W4" s="5" t="s">
+      <c r="V4" s="14"/>
+      <c r="W4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="5" t="s">
+      <c r="X4" s="14"/>
+      <c r="Y4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="5" t="s">
+      <c r="Z4" s="14"/>
+      <c r="AA4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="5" t="s">
+      <c r="AB4" s="14"/>
+      <c r="AC4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="5" t="s">
+      <c r="AD4" s="14"/>
+      <c r="AE4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AF4" s="6"/>
-      <c r="AG4" s="5" t="s">
+      <c r="AF4" s="14"/>
+      <c r="AG4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AH4" s="6"/>
-      <c r="AI4" s="5" t="s">
+      <c r="AH4" s="14"/>
+      <c r="AI4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AJ4" s="6"/>
-      <c r="AK4" s="5" t="s">
+      <c r="AJ4" s="14"/>
+      <c r="AK4" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AL4" s="7"/>
-      <c r="AM4" s="9"/>
+      <c r="AL4" s="16"/>
+      <c r="AM4" s="17"/>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A5" s="1" t="s">
@@ -2876,250 +2876,250 @@
       <c r="AM31" s="2"/>
     </row>
     <row r="32" spans="1:39" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="12"/>
-      <c r="P32" s="12"/>
-      <c r="Q32" s="12"/>
-      <c r="R32" s="12"/>
-      <c r="S32" s="12"/>
-      <c r="T32" s="12"/>
-      <c r="U32" s="12"/>
-      <c r="V32" s="12"/>
-      <c r="W32" s="12"/>
-      <c r="X32" s="12"/>
-      <c r="Y32" s="12"/>
-      <c r="Z32" s="12"/>
-      <c r="AA32" s="12"/>
-      <c r="AB32" s="12"/>
-      <c r="AC32" s="12"/>
-      <c r="AD32" s="12"/>
-      <c r="AE32" s="12"/>
-      <c r="AF32" s="12"/>
-      <c r="AG32" s="12"/>
-      <c r="AH32" s="12"/>
-      <c r="AI32" s="12"/>
-      <c r="AJ32" s="12"/>
-      <c r="AK32" s="12"/>
-      <c r="AL32" s="12"/>
-      <c r="AM32" s="13"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="6"/>
+      <c r="T32" s="6"/>
+      <c r="U32" s="6"/>
+      <c r="V32" s="6"/>
+      <c r="W32" s="6"/>
+      <c r="X32" s="6"/>
+      <c r="Y32" s="6"/>
+      <c r="Z32" s="6"/>
+      <c r="AA32" s="6"/>
+      <c r="AB32" s="6"/>
+      <c r="AC32" s="6"/>
+      <c r="AD32" s="6"/>
+      <c r="AE32" s="6"/>
+      <c r="AF32" s="6"/>
+      <c r="AG32" s="6"/>
+      <c r="AH32" s="6"/>
+      <c r="AI32" s="6"/>
+      <c r="AJ32" s="6"/>
+      <c r="AK32" s="6"/>
+      <c r="AL32" s="6"/>
+      <c r="AM32" s="7"/>
     </row>
     <row r="33" spans="1:39" ht="18.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15"/>
-      <c r="R33" s="15"/>
-      <c r="S33" s="15"/>
-      <c r="T33" s="15"/>
-      <c r="U33" s="15"/>
-      <c r="V33" s="15"/>
-      <c r="W33" s="15"/>
-      <c r="X33" s="15"/>
-      <c r="Y33" s="15"/>
-      <c r="Z33" s="15"/>
-      <c r="AA33" s="15"/>
-      <c r="AB33" s="15"/>
-      <c r="AC33" s="15"/>
-      <c r="AD33" s="15"/>
-      <c r="AE33" s="15"/>
-      <c r="AF33" s="15"/>
-      <c r="AG33" s="15"/>
-      <c r="AH33" s="15"/>
-      <c r="AI33" s="15"/>
-      <c r="AJ33" s="15"/>
-      <c r="AK33" s="15"/>
-      <c r="AL33" s="15"/>
-      <c r="AM33" s="16"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
+      <c r="Y33" s="9"/>
+      <c r="Z33" s="9"/>
+      <c r="AA33" s="9"/>
+      <c r="AB33" s="9"/>
+      <c r="AC33" s="9"/>
+      <c r="AD33" s="9"/>
+      <c r="AE33" s="9"/>
+      <c r="AF33" s="9"/>
+      <c r="AG33" s="9"/>
+      <c r="AH33" s="9"/>
+      <c r="AI33" s="9"/>
+      <c r="AJ33" s="9"/>
+      <c r="AK33" s="9"/>
+      <c r="AL33" s="9"/>
+      <c r="AM33" s="10"/>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.15">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D34" s="6"/>
-      <c r="E34" s="5" t="s">
+      <c r="D34" s="14"/>
+      <c r="E34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="5" t="s">
+      <c r="F34" s="14"/>
+      <c r="G34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="H34" s="6"/>
-      <c r="I34" s="5" t="s">
+      <c r="H34" s="14"/>
+      <c r="I34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="J34" s="6"/>
-      <c r="K34" s="5" t="s">
+      <c r="J34" s="14"/>
+      <c r="K34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="L34" s="6"/>
-      <c r="M34" s="5" t="s">
+      <c r="L34" s="14"/>
+      <c r="M34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="N34" s="6"/>
-      <c r="O34" s="5" t="s">
+      <c r="N34" s="14"/>
+      <c r="O34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="5" t="s">
+      <c r="P34" s="14"/>
+      <c r="Q34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="R34" s="6"/>
-      <c r="S34" s="5" t="s">
+      <c r="R34" s="14"/>
+      <c r="S34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="T34" s="6"/>
-      <c r="U34" s="5" t="s">
+      <c r="T34" s="14"/>
+      <c r="U34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="V34" s="6"/>
-      <c r="W34" s="5" t="s">
+      <c r="V34" s="14"/>
+      <c r="W34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="X34" s="6"/>
-      <c r="Y34" s="5" t="s">
+      <c r="X34" s="14"/>
+      <c r="Y34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="5" t="s">
+      <c r="Z34" s="14"/>
+      <c r="AA34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="AB34" s="6"/>
-      <c r="AC34" s="5" t="s">
+      <c r="AB34" s="14"/>
+      <c r="AC34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="5" t="s">
+      <c r="AD34" s="14"/>
+      <c r="AE34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="5" t="s">
+      <c r="AF34" s="14"/>
+      <c r="AG34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="5" t="s">
+      <c r="AH34" s="14"/>
+      <c r="AI34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="AJ34" s="6"/>
-      <c r="AK34" s="5" t="s">
+      <c r="AJ34" s="14"/>
+      <c r="AK34" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="AL34" s="7"/>
-      <c r="AM34" s="8" t="s">
+      <c r="AL34" s="16"/>
+      <c r="AM34" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:39" x14ac:dyDescent="0.15">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="10" t="s">
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="5" t="s">
+      <c r="D35" s="14"/>
+      <c r="E35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="F35" s="6"/>
-      <c r="G35" s="5" t="s">
+      <c r="F35" s="14"/>
+      <c r="G35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H35" s="6"/>
-      <c r="I35" s="5" t="s">
+      <c r="H35" s="14"/>
+      <c r="I35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="J35" s="6"/>
-      <c r="K35" s="5" t="s">
+      <c r="J35" s="14"/>
+      <c r="K35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="L35" s="6"/>
-      <c r="M35" s="5" t="s">
+      <c r="L35" s="14"/>
+      <c r="M35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="N35" s="6"/>
-      <c r="O35" s="5" t="s">
+      <c r="N35" s="14"/>
+      <c r="O35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="P35" s="6"/>
-      <c r="Q35" s="5" t="s">
+      <c r="P35" s="14"/>
+      <c r="Q35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="R35" s="6"/>
-      <c r="S35" s="5" t="s">
+      <c r="R35" s="14"/>
+      <c r="S35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="T35" s="6"/>
-      <c r="U35" s="5" t="s">
+      <c r="T35" s="14"/>
+      <c r="U35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="V35" s="6"/>
-      <c r="W35" s="5" t="s">
+      <c r="V35" s="14"/>
+      <c r="W35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="X35" s="6"/>
-      <c r="Y35" s="5" t="s">
+      <c r="X35" s="14"/>
+      <c r="Y35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="Z35" s="6"/>
-      <c r="AA35" s="5" t="s">
+      <c r="Z35" s="14"/>
+      <c r="AA35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AB35" s="6"/>
-      <c r="AC35" s="5" t="s">
+      <c r="AB35" s="14"/>
+      <c r="AC35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AD35" s="6"/>
-      <c r="AE35" s="5" t="s">
+      <c r="AD35" s="14"/>
+      <c r="AE35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AF35" s="6"/>
-      <c r="AG35" s="5" t="s">
+      <c r="AF35" s="14"/>
+      <c r="AG35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AH35" s="6"/>
-      <c r="AI35" s="5" t="s">
+      <c r="AH35" s="14"/>
+      <c r="AI35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AJ35" s="6"/>
-      <c r="AK35" s="5" t="s">
+      <c r="AJ35" s="14"/>
+      <c r="AK35" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AL35" s="7"/>
-      <c r="AM35" s="9"/>
+      <c r="AL35" s="16"/>
+      <c r="AM35" s="17"/>
     </row>
     <row r="36" spans="1:39" x14ac:dyDescent="0.15">
       <c r="A36" s="1" t="s">
@@ -4032,6 +4032,72 @@
     </row>
   </sheetData>
   <mergeCells count="82">
+    <mergeCell ref="AK35:AL35"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="U35:V35"/>
+    <mergeCell ref="W35:X35"/>
+    <mergeCell ref="Y35:Z35"/>
+    <mergeCell ref="AA35:AB35"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AE35:AF35"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AI35:AJ35"/>
+    <mergeCell ref="AG34:AH34"/>
+    <mergeCell ref="AI34:AJ34"/>
+    <mergeCell ref="AK34:AL34"/>
+    <mergeCell ref="AM34:AM35"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="U34:V34"/>
+    <mergeCell ref="W34:X34"/>
+    <mergeCell ref="Y34:Z34"/>
+    <mergeCell ref="AA34:AB34"/>
+    <mergeCell ref="AC34:AD34"/>
+    <mergeCell ref="AE34:AF34"/>
+    <mergeCell ref="AC4:AD4"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="AI3:AJ3"/>
+    <mergeCell ref="S34:T34"/>
+    <mergeCell ref="AG4:AH4"/>
+    <mergeCell ref="AI4:AJ4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="A32:AM32"/>
+    <mergeCell ref="A33:AM33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AA4:AB4"/>
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AM3:AM4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="AE3:AF3"/>
+    <mergeCell ref="AG3:AH3"/>
     <mergeCell ref="A1:AM1"/>
     <mergeCell ref="A2:AM2"/>
     <mergeCell ref="A3:A4"/>
@@ -4048,72 +4114,6 @@
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:X3"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="AE3:AF3"/>
-    <mergeCell ref="AG3:AH3"/>
-    <mergeCell ref="AI3:AJ3"/>
-    <mergeCell ref="S34:T34"/>
-    <mergeCell ref="AG4:AH4"/>
-    <mergeCell ref="AI4:AJ4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="A32:AM32"/>
-    <mergeCell ref="A33:AM33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AA4:AB4"/>
-    <mergeCell ref="AC4:AD4"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="AG34:AH34"/>
-    <mergeCell ref="AI34:AJ34"/>
-    <mergeCell ref="AK34:AL34"/>
-    <mergeCell ref="AM34:AM35"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="U34:V34"/>
-    <mergeCell ref="W34:X34"/>
-    <mergeCell ref="Y34:Z34"/>
-    <mergeCell ref="AA34:AB34"/>
-    <mergeCell ref="AC34:AD34"/>
-    <mergeCell ref="AE34:AF34"/>
-    <mergeCell ref="AK35:AL35"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="S35:T35"/>
-    <mergeCell ref="U35:V35"/>
-    <mergeCell ref="W35:X35"/>
-    <mergeCell ref="Y35:Z35"/>
-    <mergeCell ref="AA35:AB35"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="AE35:AF35"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AI35:AJ35"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.38" right="0.33" top="0.62" bottom="0.73" header="0.4" footer="0.35"/>
